--- a/raw/1962election.xlsx
+++ b/raw/1962election.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/admin/Dropbox/MyData/USvoting/historical voting/1920to1974/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{533FB27F-2B01-4147-9880-7BDC736078FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBED020D-DDDD-D944-A797-2C52376765D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="16440" windowHeight="16060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27881,7 +27881,7 @@
         <v>13</v>
       </c>
       <c r="D957">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E957" t="s">
         <v>1199</v>
